--- a/inputs/templates/TEMPLATE FONDO LIQUIDEZ Monetario I.xlsx
+++ b/inputs/templates/TEMPLATE FONDO LIQUIDEZ Monetario I.xlsx
@@ -25,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
@@ -35,7 +35,8 @@
     <numFmt numFmtId="170" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="171" formatCode="0.000%"/>
     <numFmt numFmtId="172" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="[$$-1004]#,##0"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="174" formatCode="[$$-1004]#,##0"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -426,7 +427,7 @@
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="29" fillId="14" borderId="2" applyAlignment="1">
+    <xf numFmtId="174" fontId="29" fillId="14" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0"/>
@@ -470,7 +471,7 @@
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -726,6 +727,8 @@
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="30" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="65">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2219,7 +2222,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2271,7 +2274,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2371,7 +2374,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -3021,7 +3024,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="es-CL"/>
             </a:p>
@@ -3053,7 +3056,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -3090,7 +3093,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -4411,7 +4414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK249"/>
+  <dimension ref="A1:BK251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.28515625" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" style="14" min="1" max="2"/>
@@ -6711,7 +6714,7 @@
         </is>
       </c>
       <c r="AW19" s="84" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="AX19" s="42">
         <f>EOMONTH($AW19,AX18)+6+1</f>
@@ -7110,8 +7113,14 @@
         <f>+S23/R23-1</f>
         <v/>
       </c>
-      <c r="AI22" s="20" t="n"/>
-      <c r="AJ22" s="20" t="n"/>
+      <c r="AI22" s="20">
+        <f>+T23/S23-1</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="20">
+        <f>+U23/T23-1</f>
+        <v/>
+      </c>
       <c r="AK22" s="20" t="n"/>
       <c r="AL22" s="20" t="n"/>
       <c r="AM22" s="20" t="n"/>
@@ -7119,7 +7128,7 @@
       <c r="AO22" s="20" t="n"/>
       <c r="AP22" s="20" t="n"/>
       <c r="AQ22" s="34">
-        <f>+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
+        <f>+(U23/P23-1)/COUNTA(AE22:AJ22)*12</f>
         <v/>
       </c>
       <c r="AV22" s="39" t="inlineStr">
@@ -7178,7 +7187,14 @@
         <f>+B249</f>
         <v/>
       </c>
-      <c r="U23" s="30" t="n"/>
+      <c r="T23">
+        <f>+B250</f>
+        <v/>
+      </c>
+      <c r="U23" s="30">
+        <f>+B251</f>
+        <v/>
+      </c>
       <c r="Y23" s="30" t="n"/>
       <c r="AD23" s="37" t="n"/>
       <c r="AE23" s="20" t="n"/>
@@ -8381,8 +8397,14 @@
         <f>+G249</f>
         <v/>
       </c>
-      <c r="T37" s="118" t="n"/>
-      <c r="U37" s="118" t="n"/>
+      <c r="T37" s="118">
+        <f>+G250</f>
+        <v/>
+      </c>
+      <c r="U37" s="118">
+        <f>+G251</f>
+        <v/>
+      </c>
       <c r="V37" s="118" t="n"/>
       <c r="W37" s="118" t="n"/>
       <c r="X37" s="118" t="n"/>
@@ -8516,8 +8538,16 @@
         <f>+(S37/R37-1)</f>
         <v/>
       </c>
+      <c r="AI38">
+        <f>+T37/S37-1</f>
+        <v/>
+      </c>
+      <c r="AJ38">
+        <f>+U37/T37-1</f>
+        <v/>
+      </c>
       <c r="AQ38" s="34">
-        <f>+(S37/P37-1)/COUNTA(AE38:AP38)*12</f>
+        <f>+(U37/P37-1)/COUNTA(AE38:AJ38)*12</f>
         <v/>
       </c>
       <c r="AR38" s="37" t="inlineStr">
@@ -10065,6 +10095,14 @@
         <f>+K249</f>
         <v/>
       </c>
+      <c r="T51">
+        <f>+K250</f>
+        <v/>
+      </c>
+      <c r="U51">
+        <f>+K251</f>
+        <v/>
+      </c>
       <c r="AD51" s="32" t="n">
         <v>2026</v>
       </c>
@@ -10084,8 +10122,14 @@
         <f>+(S51/R51-1)</f>
         <v/>
       </c>
-      <c r="AI51" s="20" t="n"/>
-      <c r="AJ51" s="20" t="n"/>
+      <c r="AI51" s="20">
+        <f>+T51/S51-1</f>
+        <v/>
+      </c>
+      <c r="AJ51" s="20">
+        <f>+U51/T51-1</f>
+        <v/>
+      </c>
       <c r="AK51" s="20" t="n"/>
       <c r="AL51" s="20" t="n"/>
       <c r="AM51" s="20" t="n"/>
@@ -10093,7 +10137,7 @@
       <c r="AO51" s="20" t="n"/>
       <c r="AP51" s="20" t="n"/>
       <c r="AQ51" s="34">
-        <f>+(S51/P51-1)/COUNTA(AE51:AP51)*12</f>
+        <f>+(U51/P51-1)/COUNTA(AE51:AJ51)*12</f>
         <v/>
       </c>
       <c r="AR51" s="20" t="n"/>
@@ -17409,6 +17453,96 @@
       </c>
       <c r="M249" s="30">
         <f>+M248*(1+L249)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="132" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B250" t="n">
+        <v>26535.18</v>
+      </c>
+      <c r="C250">
+        <f>(B250/B249-1)/(A250-A249)*30</f>
+        <v/>
+      </c>
+      <c r="D250">
+        <f>+D249*(1+C250)</f>
+        <v/>
+      </c>
+      <c r="F250" s="132" t="n">
+        <v>46173</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1152.0527</v>
+      </c>
+      <c r="H250">
+        <f>+G250+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I250">
+        <f>+(H250/H249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="J250">
+        <f>+J249*(1+I250)</f>
+        <v/>
+      </c>
+      <c r="K250" t="n">
+        <v>6368.94</v>
+      </c>
+      <c r="L250">
+        <f>+(K250/K249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="M250">
+        <f>+M249*(1+L250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="132" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B251" t="n">
+        <v>26634.69</v>
+      </c>
+      <c r="C251">
+        <f>(B251/B250-1)/(A251-A250)*30</f>
+        <v/>
+      </c>
+      <c r="D251">
+        <f>+D250*(1+C251)</f>
+        <v/>
+      </c>
+      <c r="F251" s="132" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1158.327</v>
+      </c>
+      <c r="H251">
+        <f>+G251+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I251">
+        <f>+(H251/H250-1)/(F251-F250)*30</f>
+        <v/>
+      </c>
+      <c r="J251">
+        <f>+J250*(1+I251)</f>
+        <v/>
+      </c>
+      <c r="K251" t="n">
+        <v>6385.6713</v>
+      </c>
+      <c r="L251">
+        <f>+(K251/K250-1)/(F251-F250)*30</f>
+        <v/>
+      </c>
+      <c r="M251">
+        <f>+M250*(1+L251)</f>
         <v/>
       </c>
     </row>
